--- a/cache/sepidar_food_code.xlsx
+++ b/cache/sepidar_food_code.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24701"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dorsa-Co\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\milad\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CB1918D-FE2B-4F76-B542-CF693BAF27AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A756FBA-91FE-4CE9-BBF0-7D37C7AA8E18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="17280" windowHeight="9030" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,14 +25,26 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="530">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="562">
   <si>
     <t>كد</t>
   </si>
   <si>
+    <t>1100052</t>
+  </si>
+  <si>
+    <t>1100053</t>
+  </si>
+  <si>
+    <t>1100050</t>
+  </si>
+  <si>
     <t>2800006</t>
   </si>
   <si>
+    <t>1100051</t>
+  </si>
+  <si>
     <t>2400006</t>
   </si>
   <si>
@@ -42,6 +54,9 @@
     <t>2800007</t>
   </si>
   <si>
+    <t>1100054</t>
+  </si>
+  <si>
     <t>2500045</t>
   </si>
   <si>
@@ -201,6 +216,21 @@
     <t>2300001</t>
   </si>
   <si>
+    <t>1100055</t>
+  </si>
+  <si>
+    <t>1100046</t>
+  </si>
+  <si>
+    <t>1100047</t>
+  </si>
+  <si>
+    <t>1100049</t>
+  </si>
+  <si>
+    <t>1100048</t>
+  </si>
+  <si>
     <t>2300016</t>
   </si>
   <si>
@@ -390,6 +420,9 @@
     <t>1100036</t>
   </si>
   <si>
+    <t>1100041</t>
+  </si>
+  <si>
     <t>2300024</t>
   </si>
   <si>
@@ -513,6 +546,18 @@
     <t>2700004</t>
   </si>
   <si>
+    <t>1100042</t>
+  </si>
+  <si>
+    <t>1100043</t>
+  </si>
+  <si>
+    <t>1100045</t>
+  </si>
+  <si>
+    <t>1100044</t>
+  </si>
+  <si>
     <t>2600024</t>
   </si>
   <si>
@@ -771,12 +816,12 @@
     <t>2800008</t>
   </si>
   <si>
+    <t>2800012</t>
+  </si>
+  <si>
     <t>2800001</t>
   </si>
   <si>
-    <t>2800012</t>
-  </si>
-  <si>
     <t>2800005</t>
   </si>
   <si>
@@ -786,6 +831,9 @@
     <t>1100010</t>
   </si>
   <si>
+    <t>1100040</t>
+  </si>
+  <si>
     <t>1100013</t>
   </si>
   <si>
@@ -825,9 +873,21 @@
     <t>عنوان</t>
   </si>
   <si>
+    <t>هي ي ليمويي</t>
+  </si>
+  <si>
+    <t>هي ي ساده</t>
+  </si>
+  <si>
+    <t>هي دي هلو</t>
+  </si>
+  <si>
     <t>هي دي قوطي</t>
   </si>
   <si>
+    <t>هي دي استوايي</t>
+  </si>
+  <si>
     <t>هويج</t>
   </si>
   <si>
@@ -837,6 +897,9 @@
     <t>هافنبرگ قوطي</t>
   </si>
   <si>
+    <t>هافن كاكتوس</t>
+  </si>
+  <si>
     <t>وكيوم 2 كيلويي</t>
   </si>
   <si>
@@ -996,6 +1059,21 @@
     <t>كالباس پپروني</t>
   </si>
   <si>
+    <t>قوطي ليموناد خوشگوار</t>
+  </si>
+  <si>
+    <t>قوطي كوكا</t>
+  </si>
+  <si>
+    <t>قوطي فانتا</t>
+  </si>
+  <si>
+    <t>قوطي زيرو</t>
+  </si>
+  <si>
+    <t>قوطي اسپرايت</t>
+  </si>
+  <si>
     <t>قلوگاه گوسفندي</t>
   </si>
   <si>
@@ -1185,6 +1263,9 @@
     <t>سالاد فصل فروشي</t>
   </si>
   <si>
+    <t>سالاد ژامبون و پنير</t>
+  </si>
+  <si>
     <t>ساق مرغ</t>
   </si>
   <si>
@@ -1308,6 +1389,18 @@
     <t>خمير پيتزا تك نفره</t>
   </si>
   <si>
+    <t>خانواده كوكا</t>
+  </si>
+  <si>
+    <t>خانواده فانتا</t>
+  </si>
+  <si>
+    <t>خانواده زيرو</t>
+  </si>
+  <si>
+    <t>خانواده اسپرايت</t>
+  </si>
+  <si>
     <t>خامه</t>
   </si>
   <si>
@@ -1362,9 +1455,6 @@
     <t>تايد</t>
   </si>
   <si>
-    <t>پيتزا مرغ و قارچ</t>
-  </si>
-  <si>
     <t>پيتزا مخصوص</t>
   </si>
   <si>
@@ -1566,12 +1656,12 @@
     <t>آب نارنج</t>
   </si>
   <si>
-    <t>آب معدني 300 سي سي</t>
-  </si>
-  <si>
     <t>آب معدني 1.5 ليتري</t>
   </si>
   <si>
+    <t xml:space="preserve">آب معدني </t>
+  </si>
+  <si>
     <t>آب گازدار</t>
   </si>
   <si>
@@ -1581,6 +1671,9 @@
     <t>ايتاليايي مخصوص سكه طلا</t>
   </si>
   <si>
+    <t>ايتاليايي سوسيس پسته</t>
+  </si>
+  <si>
     <t>ايتاليايي سبزيجات</t>
   </si>
   <si>
@@ -1615,6 +1708,9 @@
   </si>
   <si>
     <t>ادويه سيب</t>
+  </si>
+  <si>
+    <t>پيتزا مرغ  و قارچ</t>
   </si>
 </sst>
 </file>
@@ -1951,10 +2047,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B265"/>
+  <dimension ref="A1:B281"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="34.5703125" customWidth="1"/>
+    <col min="1" max="1" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -1962,7 +2059,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>265</v>
+        <v>281</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1970,7 +2067,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>266</v>
+        <v>282</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -1978,7 +2075,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>267</v>
+        <v>283</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -1986,7 +2083,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>268</v>
+        <v>284</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -1994,7 +2091,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>269</v>
+        <v>285</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -2002,7 +2099,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>270</v>
+        <v>286</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -2010,7 +2107,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>271</v>
+        <v>287</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -2018,7 +2115,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>272</v>
+        <v>288</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -2026,7 +2123,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>273</v>
+        <v>289</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -2034,7 +2131,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>274</v>
+        <v>290</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -2042,7 +2139,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>275</v>
+        <v>291</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -2050,7 +2147,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>276</v>
+        <v>292</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -2058,7 +2155,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>277</v>
+        <v>293</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -2066,7 +2163,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>278</v>
+        <v>294</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -2074,7 +2171,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>279</v>
+        <v>295</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -2082,7 +2179,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>280</v>
+        <v>296</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -2090,7 +2187,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>281</v>
+        <v>297</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -2098,7 +2195,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>282</v>
+        <v>298</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -2106,7 +2203,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>283</v>
+        <v>299</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -2114,7 +2211,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>284</v>
+        <v>300</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -2122,7 +2219,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>285</v>
+        <v>301</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -2130,7 +2227,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>286</v>
+        <v>302</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -2138,7 +2235,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>287</v>
+        <v>303</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -2146,7 +2243,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>288</v>
+        <v>304</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -2154,7 +2251,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>289</v>
+        <v>305</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -2162,7 +2259,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>290</v>
+        <v>306</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -2170,7 +2267,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>291</v>
+        <v>307</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -2178,7 +2275,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>292</v>
+        <v>308</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -2186,7 +2283,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>293</v>
+        <v>309</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -2194,7 +2291,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>294</v>
+        <v>310</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -2202,7 +2299,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>295</v>
+        <v>311</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -2210,7 +2307,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>296</v>
+        <v>312</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -2218,7 +2315,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>297</v>
+        <v>313</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -2226,7 +2323,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>298</v>
+        <v>314</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -2234,7 +2331,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>299</v>
+        <v>315</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -2242,7 +2339,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>300</v>
+        <v>316</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -2250,7 +2347,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>301</v>
+        <v>317</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -2258,7 +2355,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>302</v>
+        <v>318</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -2266,7 +2363,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>303</v>
+        <v>319</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -2274,7 +2371,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -2282,7 +2379,7 @@
         <v>40</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>305</v>
+        <v>321</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -2290,7 +2387,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>306</v>
+        <v>322</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -2298,7 +2395,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>307</v>
+        <v>323</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -2306,7 +2403,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>308</v>
+        <v>324</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
@@ -2314,7 +2411,7 @@
         <v>44</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>309</v>
+        <v>325</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -2322,7 +2419,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>310</v>
+        <v>326</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -2330,7 +2427,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>311</v>
+        <v>327</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -2338,7 +2435,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>312</v>
+        <v>328</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -2346,7 +2443,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>313</v>
+        <v>329</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -2354,7 +2451,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>314</v>
+        <v>330</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -2362,7 +2459,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>315</v>
+        <v>331</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -2370,7 +2467,7 @@
         <v>51</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>316</v>
+        <v>332</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -2378,7 +2475,7 @@
         <v>52</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>317</v>
+        <v>333</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -2386,7 +2483,7 @@
         <v>53</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>318</v>
+        <v>334</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -2394,7 +2491,7 @@
         <v>54</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>319</v>
+        <v>335</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
@@ -2402,7 +2499,7 @@
         <v>55</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>320</v>
+        <v>336</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
@@ -2410,7 +2507,7 @@
         <v>56</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>321</v>
+        <v>337</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
@@ -2418,7 +2515,7 @@
         <v>57</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>322</v>
+        <v>338</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
@@ -2426,7 +2523,7 @@
         <v>58</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>323</v>
+        <v>339</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
@@ -2434,7 +2531,7 @@
         <v>59</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>324</v>
+        <v>340</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
@@ -2442,7 +2539,7 @@
         <v>60</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>325</v>
+        <v>341</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
@@ -2450,7 +2547,7 @@
         <v>61</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>326</v>
+        <v>342</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
@@ -2458,7 +2555,7 @@
         <v>62</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>327</v>
+        <v>343</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
@@ -2466,7 +2563,7 @@
         <v>63</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>328</v>
+        <v>344</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
@@ -2474,7 +2571,7 @@
         <v>64</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>329</v>
+        <v>345</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
@@ -2482,7 +2579,7 @@
         <v>65</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>330</v>
+        <v>346</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
@@ -2490,7 +2587,7 @@
         <v>66</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>331</v>
+        <v>347</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
@@ -2498,7 +2595,7 @@
         <v>67</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>332</v>
+        <v>348</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
@@ -2506,7 +2603,7 @@
         <v>68</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>333</v>
+        <v>349</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
@@ -2514,7 +2611,7 @@
         <v>69</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
@@ -2522,7 +2619,7 @@
         <v>70</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>335</v>
+        <v>351</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
@@ -2530,7 +2627,7 @@
         <v>71</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>336</v>
+        <v>352</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
@@ -2538,7 +2635,7 @@
         <v>72</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>337</v>
+        <v>353</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
@@ -2546,7 +2643,7 @@
         <v>73</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>338</v>
+        <v>354</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
@@ -2554,7 +2651,7 @@
         <v>74</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>339</v>
+        <v>355</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
@@ -2562,7 +2659,7 @@
         <v>75</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>340</v>
+        <v>356</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
@@ -2570,7 +2667,7 @@
         <v>76</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>341</v>
+        <v>357</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
@@ -2578,7 +2675,7 @@
         <v>77</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>342</v>
+        <v>358</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
@@ -2586,7 +2683,7 @@
         <v>78</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>343</v>
+        <v>359</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
@@ -2594,7 +2691,7 @@
         <v>79</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>344</v>
+        <v>360</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
@@ -2602,7 +2699,7 @@
         <v>80</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>345</v>
+        <v>361</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
@@ -2610,7 +2707,7 @@
         <v>81</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>346</v>
+        <v>362</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
@@ -2618,7 +2715,7 @@
         <v>82</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>347</v>
+        <v>363</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
@@ -2626,7 +2723,7 @@
         <v>83</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>348</v>
+        <v>364</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
@@ -2634,7 +2731,7 @@
         <v>84</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>349</v>
+        <v>365</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
@@ -2642,7 +2739,7 @@
         <v>85</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>350</v>
+        <v>366</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
@@ -2650,7 +2747,7 @@
         <v>86</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>351</v>
+        <v>367</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
@@ -2658,7 +2755,7 @@
         <v>87</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>352</v>
+        <v>368</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
@@ -2666,7 +2763,7 @@
         <v>88</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>353</v>
+        <v>369</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
@@ -2674,7 +2771,7 @@
         <v>89</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>354</v>
+        <v>370</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
@@ -2682,7 +2779,7 @@
         <v>90</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>355</v>
+        <v>371</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
@@ -2690,7 +2787,7 @@
         <v>91</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>356</v>
+        <v>372</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
@@ -2698,7 +2795,7 @@
         <v>92</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>357</v>
+        <v>373</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
@@ -2706,7 +2803,7 @@
         <v>93</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>358</v>
+        <v>374</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
@@ -2714,7 +2811,7 @@
         <v>94</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>359</v>
+        <v>375</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
@@ -2722,7 +2819,7 @@
         <v>95</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>360</v>
+        <v>376</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
@@ -2730,7 +2827,7 @@
         <v>96</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>361</v>
+        <v>377</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
@@ -2738,7 +2835,7 @@
         <v>97</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>362</v>
+        <v>378</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
@@ -2746,7 +2843,7 @@
         <v>98</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>363</v>
+        <v>379</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
@@ -2754,7 +2851,7 @@
         <v>99</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>364</v>
+        <v>380</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
@@ -2762,7 +2859,7 @@
         <v>100</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>365</v>
+        <v>381</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
@@ -2770,7 +2867,7 @@
         <v>101</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>366</v>
+        <v>382</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
@@ -2778,7 +2875,7 @@
         <v>102</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>367</v>
+        <v>383</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
@@ -2786,7 +2883,7 @@
         <v>103</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>368</v>
+        <v>384</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
@@ -2794,7 +2891,7 @@
         <v>104</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>369</v>
+        <v>385</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
@@ -2802,7 +2899,7 @@
         <v>105</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>370</v>
+        <v>386</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
@@ -2810,7 +2907,7 @@
         <v>106</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>371</v>
+        <v>387</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
@@ -2818,7 +2915,7 @@
         <v>107</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>372</v>
+        <v>388</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
@@ -2826,7 +2923,7 @@
         <v>108</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>373</v>
+        <v>389</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
@@ -2834,7 +2931,7 @@
         <v>109</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>374</v>
+        <v>390</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
@@ -2842,7 +2939,7 @@
         <v>110</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>375</v>
+        <v>391</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
@@ -2850,7 +2947,7 @@
         <v>111</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>376</v>
+        <v>392</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
@@ -2858,7 +2955,7 @@
         <v>112</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>377</v>
+        <v>393</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
@@ -2866,7 +2963,7 @@
         <v>113</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>378</v>
+        <v>394</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
@@ -2874,7 +2971,7 @@
         <v>114</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>379</v>
+        <v>395</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
@@ -2882,7 +2979,7 @@
         <v>115</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>380</v>
+        <v>396</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
@@ -2890,7 +2987,7 @@
         <v>116</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>381</v>
+        <v>397</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
@@ -2898,7 +2995,7 @@
         <v>117</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>382</v>
+        <v>398</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
@@ -2906,7 +3003,7 @@
         <v>118</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>383</v>
+        <v>399</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
@@ -2914,7 +3011,7 @@
         <v>119</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>384</v>
+        <v>400</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
@@ -2922,7 +3019,7 @@
         <v>120</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>385</v>
+        <v>401</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
@@ -2930,7 +3027,7 @@
         <v>121</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>386</v>
+        <v>402</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
@@ -2938,7 +3035,7 @@
         <v>122</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>387</v>
+        <v>403</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
@@ -2946,7 +3043,7 @@
         <v>123</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>388</v>
+        <v>404</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
@@ -2954,7 +3051,7 @@
         <v>124</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>389</v>
+        <v>405</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.25">
@@ -2962,7 +3059,7 @@
         <v>125</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>390</v>
+        <v>406</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.25">
@@ -2970,7 +3067,7 @@
         <v>126</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>391</v>
+        <v>407</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.25">
@@ -2978,7 +3075,7 @@
         <v>127</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>392</v>
+        <v>408</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.25">
@@ -2986,7 +3083,7 @@
         <v>128</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>393</v>
+        <v>409</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.25">
@@ -2994,7 +3091,7 @@
         <v>129</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>394</v>
+        <v>410</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.25">
@@ -3002,7 +3099,7 @@
         <v>130</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>395</v>
+        <v>411</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.25">
@@ -3010,7 +3107,7 @@
         <v>131</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>396</v>
+        <v>412</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.25">
@@ -3018,7 +3115,7 @@
         <v>132</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>397</v>
+        <v>413</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.25">
@@ -3026,7 +3123,7 @@
         <v>133</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>398</v>
+        <v>414</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.25">
@@ -3034,7 +3131,7 @@
         <v>134</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>399</v>
+        <v>415</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.25">
@@ -3042,7 +3139,7 @@
         <v>135</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>400</v>
+        <v>416</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.25">
@@ -3050,7 +3147,7 @@
         <v>136</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>401</v>
+        <v>417</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.25">
@@ -3058,7 +3155,7 @@
         <v>137</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>402</v>
+        <v>418</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.25">
@@ -3066,7 +3163,7 @@
         <v>138</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>403</v>
+        <v>419</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.25">
@@ -3074,7 +3171,7 @@
         <v>139</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>404</v>
+        <v>420</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.25">
@@ -3082,7 +3179,7 @@
         <v>140</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>405</v>
+        <v>421</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.25">
@@ -3090,7 +3187,7 @@
         <v>141</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>406</v>
+        <v>422</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.25">
@@ -3098,7 +3195,7 @@
         <v>142</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>407</v>
+        <v>423</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.25">
@@ -3106,7 +3203,7 @@
         <v>143</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>408</v>
+        <v>424</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.25">
@@ -3114,7 +3211,7 @@
         <v>144</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>409</v>
+        <v>425</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.25">
@@ -3122,7 +3219,7 @@
         <v>145</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>410</v>
+        <v>426</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.25">
@@ -3130,7 +3227,7 @@
         <v>146</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>411</v>
+        <v>427</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.25">
@@ -3138,7 +3235,7 @@
         <v>147</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>412</v>
+        <v>428</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.25">
@@ -3146,7 +3243,7 @@
         <v>148</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>413</v>
+        <v>429</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.25">
@@ -3154,7 +3251,7 @@
         <v>149</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.25">
@@ -3162,7 +3259,7 @@
         <v>150</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>415</v>
+        <v>431</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.25">
@@ -3170,7 +3267,7 @@
         <v>151</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>416</v>
+        <v>432</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.25">
@@ -3178,7 +3275,7 @@
         <v>152</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>417</v>
+        <v>433</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.25">
@@ -3186,7 +3283,7 @@
         <v>153</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>418</v>
+        <v>434</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.25">
@@ -3194,7 +3291,7 @@
         <v>154</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>419</v>
+        <v>435</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.25">
@@ -3202,7 +3299,7 @@
         <v>155</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>420</v>
+        <v>436</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.25">
@@ -3210,7 +3307,7 @@
         <v>156</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>421</v>
+        <v>437</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.25">
@@ -3218,7 +3315,7 @@
         <v>157</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>422</v>
+        <v>438</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.25">
@@ -3226,7 +3323,7 @@
         <v>158</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>423</v>
+        <v>439</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.25">
@@ -3234,7 +3331,7 @@
         <v>159</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>424</v>
+        <v>440</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.25">
@@ -3242,7 +3339,7 @@
         <v>160</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>425</v>
+        <v>441</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.25">
@@ -3250,7 +3347,7 @@
         <v>161</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>426</v>
+        <v>442</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.25">
@@ -3258,7 +3355,7 @@
         <v>162</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>427</v>
+        <v>443</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.25">
@@ -3266,7 +3363,7 @@
         <v>163</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>428</v>
+        <v>444</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.25">
@@ -3274,7 +3371,7 @@
         <v>164</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>429</v>
+        <v>445</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.25">
@@ -3282,7 +3379,7 @@
         <v>165</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>430</v>
+        <v>446</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.25">
@@ -3290,7 +3387,7 @@
         <v>166</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>431</v>
+        <v>447</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.25">
@@ -3298,7 +3395,7 @@
         <v>167</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>432</v>
+        <v>448</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.25">
@@ -3306,7 +3403,7 @@
         <v>168</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>433</v>
+        <v>449</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.25">
@@ -3314,7 +3411,7 @@
         <v>169</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>434</v>
+        <v>450</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.25">
@@ -3322,7 +3419,7 @@
         <v>170</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>435</v>
+        <v>451</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.25">
@@ -3330,7 +3427,7 @@
         <v>171</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>436</v>
+        <v>452</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.25">
@@ -3338,7 +3435,7 @@
         <v>172</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>437</v>
+        <v>453</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.25">
@@ -3346,7 +3443,7 @@
         <v>173</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>438</v>
+        <v>454</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.25">
@@ -3354,7 +3451,7 @@
         <v>174</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>439</v>
+        <v>455</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.25">
@@ -3362,7 +3459,7 @@
         <v>175</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>440</v>
+        <v>456</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.25">
@@ -3370,7 +3467,7 @@
         <v>176</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>441</v>
+        <v>457</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.25">
@@ -3378,7 +3475,7 @@
         <v>177</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>442</v>
+        <v>458</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.25">
@@ -3386,7 +3483,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>443</v>
+        <v>459</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.25">
@@ -3394,7 +3491,7 @@
         <v>179</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>444</v>
+        <v>460</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.25">
@@ -3402,7 +3499,7 @@
         <v>180</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>445</v>
+        <v>461</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.25">
@@ -3410,7 +3507,7 @@
         <v>181</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>446</v>
+        <v>462</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.25">
@@ -3418,7 +3515,7 @@
         <v>182</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>447</v>
+        <v>463</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.25">
@@ -3426,7 +3523,7 @@
         <v>183</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>448</v>
+        <v>464</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.25">
@@ -3434,7 +3531,7 @@
         <v>184</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>449</v>
+        <v>465</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.25">
@@ -3442,7 +3539,7 @@
         <v>185</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>450</v>
+        <v>466</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.25">
@@ -3450,7 +3547,7 @@
         <v>186</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>451</v>
+        <v>467</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.25">
@@ -3458,7 +3555,7 @@
         <v>187</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>452</v>
+        <v>468</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.25">
@@ -3466,7 +3563,7 @@
         <v>188</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>453</v>
+        <v>469</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.25">
@@ -3474,7 +3571,7 @@
         <v>189</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>454</v>
+        <v>470</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.25">
@@ -3482,7 +3579,7 @@
         <v>190</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>455</v>
+        <v>471</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.25">
@@ -3490,7 +3587,7 @@
         <v>191</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>456</v>
+        <v>472</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.25">
@@ -3498,7 +3595,7 @@
         <v>192</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>457</v>
+        <v>473</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.25">
@@ -3506,7 +3603,7 @@
         <v>193</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>458</v>
+        <v>474</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.25">
@@ -3514,7 +3611,7 @@
         <v>194</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>459</v>
+        <v>475</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.25">
@@ -3522,7 +3619,7 @@
         <v>195</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>460</v>
+        <v>561</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.25">
@@ -3530,7 +3627,7 @@
         <v>196</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>461</v>
+        <v>476</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.25">
@@ -3538,7 +3635,7 @@
         <v>197</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>462</v>
+        <v>477</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.25">
@@ -3546,7 +3643,7 @@
         <v>198</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>463</v>
+        <v>478</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.25">
@@ -3554,7 +3651,7 @@
         <v>199</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>464</v>
+        <v>479</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.25">
@@ -3562,7 +3659,7 @@
         <v>200</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>465</v>
+        <v>480</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.25">
@@ -3570,7 +3667,7 @@
         <v>201</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>466</v>
+        <v>481</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.25">
@@ -3578,7 +3675,7 @@
         <v>202</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>467</v>
+        <v>482</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.25">
@@ -3586,7 +3683,7 @@
         <v>203</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>468</v>
+        <v>483</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.25">
@@ -3594,7 +3691,7 @@
         <v>204</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>469</v>
+        <v>484</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.25">
@@ -3602,7 +3699,7 @@
         <v>205</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>470</v>
+        <v>485</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.25">
@@ -3610,7 +3707,7 @@
         <v>206</v>
       </c>
       <c r="B207" s="3" t="s">
-        <v>471</v>
+        <v>486</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.25">
@@ -3618,7 +3715,7 @@
         <v>207</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>472</v>
+        <v>487</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.25">
@@ -3626,7 +3723,7 @@
         <v>208</v>
       </c>
       <c r="B209" s="3" t="s">
-        <v>473</v>
+        <v>488</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.25">
@@ -3634,7 +3731,7 @@
         <v>209</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>474</v>
+        <v>489</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.25">
@@ -3642,7 +3739,7 @@
         <v>210</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>475</v>
+        <v>490</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.25">
@@ -3650,7 +3747,7 @@
         <v>211</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>476</v>
+        <v>491</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.25">
@@ -3658,7 +3755,7 @@
         <v>212</v>
       </c>
       <c r="B213" s="3" t="s">
-        <v>477</v>
+        <v>492</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.25">
@@ -3666,7 +3763,7 @@
         <v>213</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>478</v>
+        <v>493</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.25">
@@ -3674,7 +3771,7 @@
         <v>214</v>
       </c>
       <c r="B215" s="3" t="s">
-        <v>479</v>
+        <v>494</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.25">
@@ -3682,7 +3779,7 @@
         <v>215</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>480</v>
+        <v>495</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.25">
@@ -3690,7 +3787,7 @@
         <v>216</v>
       </c>
       <c r="B217" s="3" t="s">
-        <v>481</v>
+        <v>496</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.25">
@@ -3698,7 +3795,7 @@
         <v>217</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>482</v>
+        <v>497</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.25">
@@ -3706,7 +3803,7 @@
         <v>218</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>483</v>
+        <v>498</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.25">
@@ -3714,7 +3811,7 @@
         <v>219</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>484</v>
+        <v>499</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.25">
@@ -3722,7 +3819,7 @@
         <v>220</v>
       </c>
       <c r="B221" s="3" t="s">
-        <v>485</v>
+        <v>500</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.25">
@@ -3730,7 +3827,7 @@
         <v>221</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>486</v>
+        <v>501</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.25">
@@ -3738,7 +3835,7 @@
         <v>222</v>
       </c>
       <c r="B223" s="3" t="s">
-        <v>487</v>
+        <v>502</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.25">
@@ -3746,7 +3843,7 @@
         <v>223</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>488</v>
+        <v>503</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.25">
@@ -3754,7 +3851,7 @@
         <v>224</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>489</v>
+        <v>504</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.25">
@@ -3762,7 +3859,7 @@
         <v>225</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>490</v>
+        <v>505</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.25">
@@ -3770,7 +3867,7 @@
         <v>226</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>491</v>
+        <v>506</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.25">
@@ -3778,7 +3875,7 @@
         <v>227</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>492</v>
+        <v>507</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.25">
@@ -3786,7 +3883,7 @@
         <v>228</v>
       </c>
       <c r="B229" s="3" t="s">
-        <v>493</v>
+        <v>508</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.25">
@@ -3794,7 +3891,7 @@
         <v>229</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>494</v>
+        <v>509</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.25">
@@ -3802,7 +3899,7 @@
         <v>230</v>
       </c>
       <c r="B231" s="3" t="s">
-        <v>495</v>
+        <v>510</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.25">
@@ -3810,7 +3907,7 @@
         <v>231</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>496</v>
+        <v>511</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.25">
@@ -3818,7 +3915,7 @@
         <v>232</v>
       </c>
       <c r="B233" s="3" t="s">
-        <v>497</v>
+        <v>512</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.25">
@@ -3826,7 +3923,7 @@
         <v>233</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>498</v>
+        <v>513</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.25">
@@ -3834,7 +3931,7 @@
         <v>234</v>
       </c>
       <c r="B235" s="3" t="s">
-        <v>499</v>
+        <v>514</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.25">
@@ -3842,7 +3939,7 @@
         <v>235</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>500</v>
+        <v>515</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.25">
@@ -3850,7 +3947,7 @@
         <v>236</v>
       </c>
       <c r="B237" s="3" t="s">
-        <v>501</v>
+        <v>516</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.25">
@@ -3858,7 +3955,7 @@
         <v>237</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>502</v>
+        <v>517</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.25">
@@ -3866,7 +3963,7 @@
         <v>238</v>
       </c>
       <c r="B239" s="3" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.25">
@@ -3874,7 +3971,7 @@
         <v>239</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>504</v>
+        <v>519</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.25">
@@ -3882,7 +3979,7 @@
         <v>240</v>
       </c>
       <c r="B241" s="3" t="s">
-        <v>505</v>
+        <v>520</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.25">
@@ -3890,7 +3987,7 @@
         <v>241</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>506</v>
+        <v>521</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.25">
@@ -3898,7 +3995,7 @@
         <v>242</v>
       </c>
       <c r="B243" s="3" t="s">
-        <v>507</v>
+        <v>522</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.25">
@@ -3906,7 +4003,7 @@
         <v>243</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>508</v>
+        <v>523</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.25">
@@ -3914,7 +4011,7 @@
         <v>244</v>
       </c>
       <c r="B245" s="3" t="s">
-        <v>509</v>
+        <v>524</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.25">
@@ -3922,7 +4019,7 @@
         <v>245</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>510</v>
+        <v>525</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.25">
@@ -3930,7 +4027,7 @@
         <v>246</v>
       </c>
       <c r="B247" s="3" t="s">
-        <v>511</v>
+        <v>526</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.25">
@@ -3938,7 +4035,7 @@
         <v>247</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>512</v>
+        <v>527</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.25">
@@ -3946,7 +4043,7 @@
         <v>248</v>
       </c>
       <c r="B249" s="3" t="s">
-        <v>513</v>
+        <v>528</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.25">
@@ -3954,7 +4051,7 @@
         <v>249</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>514</v>
+        <v>529</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.25">
@@ -3962,7 +4059,7 @@
         <v>250</v>
       </c>
       <c r="B251" s="3" t="s">
-        <v>515</v>
+        <v>530</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.25">
@@ -3970,7 +4067,7 @@
         <v>251</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>516</v>
+        <v>531</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.25">
@@ -3978,7 +4075,7 @@
         <v>252</v>
       </c>
       <c r="B253" s="3" t="s">
-        <v>517</v>
+        <v>532</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.25">
@@ -3986,7 +4083,7 @@
         <v>253</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>518</v>
+        <v>533</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.25">
@@ -3994,7 +4091,7 @@
         <v>254</v>
       </c>
       <c r="B255" s="3" t="s">
-        <v>519</v>
+        <v>534</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.25">
@@ -4002,7 +4099,7 @@
         <v>255</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>520</v>
+        <v>535</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.25">
@@ -4010,7 +4107,7 @@
         <v>256</v>
       </c>
       <c r="B257" s="3" t="s">
-        <v>521</v>
+        <v>536</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.25">
@@ -4018,7 +4115,7 @@
         <v>257</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>522</v>
+        <v>537</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.25">
@@ -4026,7 +4123,7 @@
         <v>258</v>
       </c>
       <c r="B259" s="3" t="s">
-        <v>523</v>
+        <v>538</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.25">
@@ -4034,7 +4131,7 @@
         <v>259</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>524</v>
+        <v>539</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.25">
@@ -4042,7 +4139,7 @@
         <v>260</v>
       </c>
       <c r="B261" s="3" t="s">
-        <v>525</v>
+        <v>540</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.25">
@@ -4050,7 +4147,7 @@
         <v>261</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>526</v>
+        <v>541</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.25">
@@ -4058,7 +4155,7 @@
         <v>262</v>
       </c>
       <c r="B263" s="3" t="s">
-        <v>527</v>
+        <v>542</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.25">
@@ -4066,7 +4163,7 @@
         <v>263</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>528</v>
+        <v>543</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.25">
@@ -4074,7 +4171,135 @@
         <v>264</v>
       </c>
       <c r="B265" s="3" t="s">
-        <v>529</v>
+        <v>544</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A266" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="B266" s="2" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A267" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="B267" s="3" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A268" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="B268" s="2" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A269" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B269" s="3" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A270" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="B270" s="2" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A271" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="B271" s="3" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A272" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="B272" s="2" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A273" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="B273" s="3" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A274" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="B274" s="2" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A275" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="B275" s="3" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A276" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="B276" s="2" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A277" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="B277" s="3" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A278" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="B278" s="2" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A279" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="B279" s="3" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A280" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="B280" s="2" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A281" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="B281" s="3" t="s">
+        <v>560</v>
       </c>
     </row>
   </sheetData>
